--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0170.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0170.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Nếu giờ ta đến quán Shashou, liệu có gặp được bọn họ không nhỉ?</t>
+          <t>Nếu giờ tao đến quán Shashou, liệu có gặp được bọn họ không nhỉ?</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>?i? ra?!</t>
+          <t>Cút… ra—!</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nói dài dòng thế. Ta biết một người thông minh và sắc sảo như cậu sẽ phá đảo trò này trong nháy mắt. Nhưng khi hoàn thành một trò chơi, ai mà chẳng hơi xúc động một chút, đúng không?</t>
+          <t>Nói dài dòng thế. Tao biết một người thông minh và sắc sảo như cậu sẽ phá đảo trò này trong nháy mắt. Nhưng khi hoàn thành một trò chơi, ai mà chẳng hơi xúc động một chút, đúng không?</t>
         </is>
       </c>
     </row>
